--- a/data/out/people.xlsx
+++ b/data/out/people.xlsx
@@ -419,13 +419,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,119 +443,89 @@
           <t>city</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Артём</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artem@example.com</t>
+          <t>SPB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Алиса</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>alice@example.com</t>
+          <t>Moscow</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Борис</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Казань</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>boris@example.com</t>
+          <t>Kazan</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Новосибирск</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>maria@example.com</t>
+          <t>SPB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Andrey</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ivan@example.com</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
     </row>
